--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-30T05:42:02.037Z</t>
+    <t>2026-08-13T00:31:36.244Z</t>
   </si>
   <si>
     <t>Medical Devices &amp; Services | DonJoy | Aircast | Exos | Procare | Compex | Chattanooga | Enovis Surgical | Dr. Comfort | CMF | Enovis</t>
